--- a/data/trans_orig/P1421-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1421-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de migrañas en 2007</t>
+          <t>Población con diagnóstico de migrañas/ jaquecas / cefaleas crónicas / dolor de cabeza frecuente en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13136</t>
+          <t>12107</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8762</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24263</t>
+          <t>24008</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13709</t>
+          <t>13068</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31390</t>
+          <t>31545</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>480928</t>
+          <t>481957</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>492244</t>
+          <t>492211</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>443226</t>
+          <t>443481</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>458727</t>
+          <t>458475</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>930163</t>
+          <t>930008</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>947844</t>
+          <t>948485</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>8916</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24547</t>
+          <t>24714</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35332</t>
+          <t>35341</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62172</t>
+          <t>61814</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47380</t>
+          <t>48750</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79095</t>
+          <t>80681</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>710942</t>
+          <t>710775</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>726802</t>
+          <t>726573</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>563322</t>
+          <t>563680</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>590162</t>
+          <t>590153</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1281887</t>
+          <t>1280301</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1313602</t>
+          <t>1312232</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>8049</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23216</t>
+          <t>22090</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30505</t>
+          <t>31610</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56321</t>
+          <t>57329</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42088</t>
+          <t>41363</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71979</t>
+          <t>71440</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>615452</t>
+          <t>616578</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>631039</t>
+          <t>630619</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>633423</t>
+          <t>632415</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>659239</t>
+          <t>658134</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1256433</t>
+          <t>1256972</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1286324</t>
+          <t>1287049</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24832</t>
+          <t>24857</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22564</t>
+          <t>21888</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43959</t>
+          <t>42861</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33457</t>
+          <t>34727</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60928</t>
+          <t>61346</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>494315</t>
+          <t>494290</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>511298</t>
+          <t>510683</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>471683</t>
+          <t>472781</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>493078</t>
+          <t>493754</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>973861</t>
+          <t>973443</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1001332</t>
+          <t>1000062</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9658</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26909</t>
+          <t>26243</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14477</t>
+          <t>14266</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33557</t>
+          <t>32723</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26755</t>
+          <t>27516</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>359801</t>
+          <t>360467</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>377052</t>
+          <t>377389</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>370429</t>
+          <t>371263</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>389509</t>
+          <t>389720</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>739551</t>
+          <t>738669</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>763941</t>
+          <t>763180</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13835</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15940</t>
+          <t>16463</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34709</t>
+          <t>36056</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22208</t>
+          <t>22643</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44721</t>
+          <t>44169</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>278748</t>
+          <t>279481</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>288928</t>
+          <t>288995</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>308225</t>
+          <t>306878</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>326994</t>
+          <t>326471</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>590796</t>
+          <t>591348</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>613309</t>
+          <t>612874</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12154</t>
+          <t>11980</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>5847</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20141</t>
+          <t>20247</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10634</t>
+          <t>9925</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26896</t>
+          <t>27970</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>197729</t>
+          <t>197903</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>207917</t>
+          <t>207935</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>313767</t>
+          <t>313661</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>328055</t>
+          <t>328061</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>516895</t>
+          <t>515821</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>533157</t>
+          <t>533866</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>62180</t>
+          <t>62800</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>97126</t>
+          <t>98230</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>168059</t>
+          <t>170511</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>221885</t>
+          <t>224671</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>242222</t>
+          <t>243028</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>307169</t>
+          <t>305286</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3179417</t>
+          <t>3178313</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3214363</t>
+          <t>3213743</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3157312</t>
+          <t>3154526</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3211138</t>
+          <t>3208686</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6348572</t>
+          <t>6350455</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6413519</t>
+          <t>6412713</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de migrañas en 2012</t>
+          <t>Población con diagnóstico de migrañas/ jaquecas / cefaleas crónicas / dolor de cabeza frecuente en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13978</t>
+          <t>13980</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24985</t>
+          <t>26285</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>13537</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33196</t>
+          <t>32245</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>440168</t>
+          <t>440166</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>451286</t>
+          <t>451000</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>405245</t>
+          <t>403945</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>422291</t>
+          <t>422221</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>851180</t>
+          <t>852131</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>871074</t>
+          <t>870839</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13979</t>
+          <t>13838</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13540</t>
+          <t>14215</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31649</t>
+          <t>33790</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20201</t>
+          <t>19723</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41052</t>
+          <t>41919</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>673108</t>
+          <t>673249</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>683470</t>
+          <t>683480</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>578606</t>
+          <t>576465</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>596715</t>
+          <t>596040</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1256290</t>
+          <t>1255423</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1277141</t>
+          <t>1277619</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>5395</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20971</t>
+          <t>20599</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38261</t>
+          <t>37829</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65474</t>
+          <t>65568</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47425</t>
+          <t>47200</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79092</t>
+          <t>78672</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>660892</t>
+          <t>661264</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>675852</t>
+          <t>676468</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>644100</t>
+          <t>644006</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>671313</t>
+          <t>671745</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1312345</t>
+          <t>1312765</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1344012</t>
+          <t>1344237</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>2953</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13363</t>
+          <t>13364</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23344</t>
+          <t>23503</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47585</t>
+          <t>48394</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27977</t>
+          <t>28993</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56070</t>
+          <t>55417</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>601254</t>
+          <t>601253</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>611697</t>
+          <t>611664</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>566679</t>
+          <t>565870</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>590920</t>
+          <t>590761</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1172810</t>
+          <t>1173463</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1200903</t>
+          <t>1199887</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10450</t>
+          <t>10041</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13865</t>
+          <t>13522</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32662</t>
+          <t>32979</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>17851</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>39765</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>417949</t>
+          <t>418358</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>427300</t>
+          <t>427355</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>415138</t>
+          <t>414821</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>433935</t>
+          <t>434278</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>837582</t>
+          <t>836434</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>858938</t>
+          <t>858348</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>985</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>8281</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14671</t>
+          <t>15446</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31891</t>
+          <t>33089</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>17816</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37445</t>
+          <t>37860</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>301346</t>
+          <t>301505</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>308819</t>
+          <t>308801</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>322105</t>
+          <t>320907</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>339325</t>
+          <t>338550</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>626337</t>
+          <t>625922</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>646521</t>
+          <t>645966</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15076</t>
+          <t>15081</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36087</t>
+          <t>34815</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16711</t>
+          <t>17515</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39205</t>
+          <t>38793</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>243134</t>
+          <t>242130</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>352892</t>
+          <t>354164</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>373903</t>
+          <t>373898</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>599625</t>
+          <t>600037</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>622119</t>
+          <t>621315</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30269</t>
+          <t>30012</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56895</t>
+          <t>55803</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>164439</t>
+          <t>166549</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>218165</t>
+          <t>217776</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>200918</t>
+          <t>202730</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>263521</t>
+          <t>263268</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3368853</t>
+          <t>3369945</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3395479</t>
+          <t>3395736</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3336933</t>
+          <t>3337322</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3390659</t>
+          <t>3388549</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6717326</t>
+          <t>6717579</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6779929</t>
+          <t>6778117</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de migrañas en 2016</t>
+          <t>Población con diagnóstico de migrañas/ jaquecas / cefaleas crónicas / dolor de cabeza frecuente en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>974</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9968</t>
+          <t>9017</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15440</t>
+          <t>15814</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6865</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19764</t>
+          <t>21062</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>409495</t>
+          <t>410446</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>418499</t>
+          <t>418489</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>380315</t>
+          <t>379941</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>391891</t>
+          <t>391497</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>795454</t>
+          <t>794156</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>808353</t>
+          <t>808304</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10533</t>
+          <t>10878</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25991</t>
+          <t>27259</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49809</t>
+          <t>51063</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30073</t>
+          <t>30811</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55308</t>
+          <t>55717</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>579963</t>
+          <t>579618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>589473</t>
+          <t>589446</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>513735</t>
+          <t>512481</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>537553</t>
+          <t>536285</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1098732</t>
+          <t>1098323</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1123967</t>
+          <t>1123229</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15745</t>
+          <t>15963</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12433</t>
+          <t>12033</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31307</t>
+          <t>31401</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17965</t>
+          <t>18133</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39820</t>
+          <t>42358</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>653352</t>
+          <t>653134</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>666047</t>
+          <t>665929</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>630079</t>
+          <t>629985</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>648953</t>
+          <t>649353</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1290663</t>
+          <t>1288125</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1312518</t>
+          <t>1312350</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6085</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20477</t>
+          <t>20216</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24148</t>
+          <t>23829</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47651</t>
+          <t>47510</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33810</t>
+          <t>34624</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60810</t>
+          <t>62240</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>625571</t>
+          <t>625832</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>639963</t>
+          <t>639949</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>601426</t>
+          <t>601567</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>624929</t>
+          <t>625248</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1234315</t>
+          <t>1232885</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1261315</t>
+          <t>1260501</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>18876</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23734</t>
+          <t>23649</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48286</t>
+          <t>48154</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34217</t>
+          <t>33895</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62067</t>
+          <t>62777</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>457886</t>
+          <t>459042</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>472785</t>
+          <t>472681</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>448563</t>
+          <t>448695</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>473115</t>
+          <t>473200</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>912700</t>
+          <t>911990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>940550</t>
+          <t>940872</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9292</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16586</t>
+          <t>16487</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35223</t>
+          <t>35331</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19916</t>
+          <t>19142</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40350</t>
+          <t>39311</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>325038</t>
+          <t>324218</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>333316</t>
+          <t>333321</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>342539</t>
+          <t>342431</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>361176</t>
+          <t>361275</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>671742</t>
+          <t>672781</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>692176</t>
+          <t>692950</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12177</t>
+          <t>12218</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24452</t>
+          <t>23834</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49337</t>
+          <t>48214</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28725</t>
+          <t>28830</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55389</t>
+          <t>55493</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>244821</t>
+          <t>244780</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>254381</t>
+          <t>254367</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>350832</t>
+          <t>351955</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>375717</t>
+          <t>376335</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>601778</t>
+          <t>601674</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>628442</t>
+          <t>628337</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>35744</t>
+          <t>35392</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>62504</t>
+          <t>62858</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>165825</t>
+          <t>169038</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>221531</t>
+          <t>225855</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>209681</t>
+          <t>211957</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>274692</t>
+          <t>280336</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3331846</t>
+          <t>3331492</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3358606</t>
+          <t>3358958</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3323011</t>
+          <t>3318687</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3378717</t>
+          <t>3375504</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6664200</t>
+          <t>6658556</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6729211</t>
+          <t>6726935</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de migrañas en 2023</t>
+          <t>Población con diagnóstico de migrañas/ jaquecas / cefaleas crónicas / dolor de cabeza frecuente en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29954</t>
+          <t>29997</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20624</t>
+          <t>19603</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48134</t>
+          <t>48410</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29599</t>
+          <t>28981</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67431</t>
+          <t>67851</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>369868</t>
+          <t>369825</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>395633</t>
+          <t>395430</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>265066</t>
+          <t>264790</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>292576</t>
+          <t>293597</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>645591</t>
+          <t>645171</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>683423</t>
+          <t>684041</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,94%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11348</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35800</t>
+          <t>33225</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30449</t>
+          <t>29823</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67474</t>
+          <t>66597</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49518</t>
+          <t>51646</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>88979</t>
+          <t>90949</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>387747</t>
+          <t>390322</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>412156</t>
+          <t>412199</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>444030</t>
+          <t>444907</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>481055</t>
+          <t>481681</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>846072</t>
+          <t>844102</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>885533</t>
+          <t>883405</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19592</t>
+          <t>20470</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43501</t>
+          <t>43923</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45717</t>
+          <t>45226</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68288</t>
+          <t>69034</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71392</t>
+          <t>72033</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104645</t>
+          <t>104824</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>492837</t>
+          <t>492415</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>516746</t>
+          <t>515868</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>472085</t>
+          <t>471339</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>494656</t>
+          <t>495147</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>972067</t>
+          <t>971888</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1005320</t>
+          <t>1004679</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18009</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65433</t>
+          <t>65574</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85933</t>
+          <t>86707</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123425</t>
+          <t>124822</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88077</t>
+          <t>90288</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>181356</t>
+          <t>183963</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>821297</t>
+          <t>821156</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>868572</t>
+          <t>868721</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>588339</t>
+          <t>586942</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>625831</t>
+          <t>625057</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1417138</t>
+          <t>1414531</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1510417</t>
+          <t>1508206</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15557</t>
+          <t>16340</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34302</t>
+          <t>34390</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55507</t>
+          <t>54427</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>78540</t>
+          <t>77659</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75719</t>
+          <t>76686</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>104982</t>
+          <t>106526</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>525935</t>
+          <t>525847</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>544680</t>
+          <t>543897</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>466188</t>
+          <t>467069</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>489221</t>
+          <t>490301</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>999982</t>
+          <t>998438</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1029245</t>
+          <t>1028278</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,06%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20796</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14405</t>
+          <t>14420</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57375</t>
+          <t>58053</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22757</t>
+          <t>24929</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>64704</t>
+          <t>65129</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>346651</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>358948</t>
+          <t>359546</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>550993</t>
+          <t>550315</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>593963</t>
+          <t>593948</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>911110</t>
+          <t>910685</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>953057</t>
+          <t>950885</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16792</t>
+          <t>17557</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35596</t>
+          <t>34862</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53200</t>
+          <t>51836</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>45922</t>
+          <t>45432</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65888</t>
+          <t>66424</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>265967</t>
+          <t>265202</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>275609</t>
+          <t>275489</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>372031</t>
+          <t>373395</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>389635</t>
+          <t>390369</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>642102</t>
+          <t>641566</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>662068</t>
+          <t>662558</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>116210</t>
+          <t>115766</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>183145</t>
+          <t>182537</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>324136</t>
+          <t>325032</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>430274</t>
+          <t>430155</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>468767</t>
+          <t>470235</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>596982</t>
+          <t>597952</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3273735</t>
+          <t>3274343</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3340670</t>
+          <t>3341114</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3224894</t>
+          <t>3225013</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3331032</t>
+          <t>3330136</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6515066</t>
+          <t>6514096</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6643281</t>
+          <t>6641813</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1421-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1421-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12107</t>
+          <t>14969</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9014</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24008</t>
+          <t>24181</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13068</t>
+          <t>13372</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31545</t>
+          <t>31334</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>481957</t>
+          <t>479095</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>492211</t>
+          <t>492166</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>443481</t>
+          <t>443308</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>458475</t>
+          <t>458493</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>930008</t>
+          <t>930219</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>948485</t>
+          <t>948181</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8916</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24714</t>
+          <t>23712</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35341</t>
+          <t>35131</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61814</t>
+          <t>62614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48750</t>
+          <t>47854</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80681</t>
+          <t>79118</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>710775</t>
+          <t>711777</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>726573</t>
+          <t>726593</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>563680</t>
+          <t>562880</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>590153</t>
+          <t>590363</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1280301</t>
+          <t>1281864</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1312232</t>
+          <t>1313128</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8049</t>
+          <t>7607</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22090</t>
+          <t>22432</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31610</t>
+          <t>30123</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57329</t>
+          <t>56368</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41363</t>
+          <t>41804</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71440</t>
+          <t>70249</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>616578</t>
+          <t>616236</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>630619</t>
+          <t>631061</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>632415</t>
+          <t>633376</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>658134</t>
+          <t>659621</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1256972</t>
+          <t>1258163</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1287049</t>
+          <t>1286608</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24857</t>
+          <t>23927</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21888</t>
+          <t>21712</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42861</t>
+          <t>42232</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34727</t>
+          <t>32689</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61346</t>
+          <t>60251</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>494290</t>
+          <t>495220</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>510683</t>
+          <t>511263</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>472781</t>
+          <t>473410</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>493754</t>
+          <t>493930</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>973443</t>
+          <t>974538</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1000062</t>
+          <t>1002100</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26243</t>
+          <t>26227</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14266</t>
+          <t>14388</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32723</t>
+          <t>33137</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27516</t>
+          <t>27467</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52027</t>
+          <t>52322</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>360467</t>
+          <t>360483</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>377389</t>
+          <t>377603</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>371263</t>
+          <t>370849</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>389720</t>
+          <t>389598</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>738669</t>
+          <t>738374</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>763180</t>
+          <t>763229</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>13320</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16463</t>
+          <t>16643</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36056</t>
+          <t>35005</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22643</t>
+          <t>22991</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44169</t>
+          <t>45064</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279481</t>
+          <t>279263</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>288995</t>
+          <t>289385</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>306878</t>
+          <t>307929</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>326471</t>
+          <t>326291</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>591348</t>
+          <t>590453</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>612874</t>
+          <t>612526</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11980</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5847</t>
+          <t>5849</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20247</t>
+          <t>20991</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>10015</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27970</t>
+          <t>27296</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>197903</t>
+          <t>198060</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>207935</t>
+          <t>207928</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>313661</t>
+          <t>312917</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>328061</t>
+          <t>328059</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>515821</t>
+          <t>516495</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>533866</t>
+          <t>533776</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>62800</t>
+          <t>63733</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>98230</t>
+          <t>98843</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>170511</t>
+          <t>168324</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>224671</t>
+          <t>222270</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>243028</t>
+          <t>241953</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>305286</t>
+          <t>304359</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3178313</t>
+          <t>3177700</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3213743</t>
+          <t>3212810</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3154526</t>
+          <t>3156927</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3208686</t>
+          <t>3210873</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6350455</t>
+          <t>6351382</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6412713</t>
+          <t>6413788</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13980</t>
+          <t>14651</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8009</t>
+          <t>7906</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26285</t>
+          <t>24199</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13537</t>
+          <t>13259</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32245</t>
+          <t>33620</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>440166</t>
+          <t>439495</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>451000</t>
+          <t>451266</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>403945</t>
+          <t>406031</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>422221</t>
+          <t>422324</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>852131</t>
+          <t>850756</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>870839</t>
+          <t>871117</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13838</t>
+          <t>13886</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14215</t>
+          <t>13707</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33790</t>
+          <t>32739</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19723</t>
+          <t>20210</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41919</t>
+          <t>40479</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>673249</t>
+          <t>673201</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>683480</t>
+          <t>683731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>576465</t>
+          <t>577516</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>596040</t>
+          <t>596548</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1255423</t>
+          <t>1256863</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1277619</t>
+          <t>1277132</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20599</t>
+          <t>20973</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37829</t>
+          <t>37636</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65568</t>
+          <t>64928</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47200</t>
+          <t>46450</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78672</t>
+          <t>78273</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>661264</t>
+          <t>660890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>676468</t>
+          <t>675894</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>644006</t>
+          <t>644646</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>671745</t>
+          <t>671938</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1312765</t>
+          <t>1313164</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1344237</t>
+          <t>1344987</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2953</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13364</t>
+          <t>12421</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23503</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48394</t>
+          <t>47920</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28993</t>
+          <t>28527</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55417</t>
+          <t>55276</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>601253</t>
+          <t>602196</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>611664</t>
+          <t>612553</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>565870</t>
+          <t>566344</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>590761</t>
+          <t>590798</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1173463</t>
+          <t>1173604</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1199887</t>
+          <t>1200353</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10041</t>
+          <t>9834</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13522</t>
+          <t>14417</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32979</t>
+          <t>33066</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17851</t>
+          <t>17492</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39765</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>418358</t>
+          <t>418565</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>427355</t>
+          <t>427343</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>414821</t>
+          <t>414734</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>434278</t>
+          <t>433383</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>836434</t>
+          <t>838023</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>858348</t>
+          <t>858707</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>981</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5447,77 +5447,77 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>22835</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>14618</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>32695</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>6,45%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>9,24%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>25923</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>17715</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>36937</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>2,67%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>22835</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>15446</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>33089</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>9,35%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>25923</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>17816</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>37860</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>301505</t>
+          <t>301360</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>308801</t>
+          <t>308805</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,82 +5555,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>97,28%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>331161</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>321301</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>339378</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>93,55%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>90,76%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>95,87%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>637859</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>626845</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>646067</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>96,09%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>94,44%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>97,33%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>331161</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>320907</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>338550</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>93,55%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>90,65%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>95,64%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>637859</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>625922</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>645966</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>96,09%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>94,3%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7721</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15081</t>
+          <t>16318</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34815</t>
+          <t>36615</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17515</t>
+          <t>17318</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38793</t>
+          <t>39014</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>242130</t>
+          <t>242546</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>354164</t>
+          <t>352364</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>373898</t>
+          <t>372661</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>600037</t>
+          <t>599816</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>621315</t>
+          <t>621512</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30012</t>
+          <t>30091</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55803</t>
+          <t>56183</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>166549</t>
+          <t>162510</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>217776</t>
+          <t>218997</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>202730</t>
+          <t>201953</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>263268</t>
+          <t>262877</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3369945</t>
+          <t>3369565</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3395736</t>
+          <t>3395657</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3337322</t>
+          <t>3336101</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3388549</t>
+          <t>3392588</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6717579</t>
+          <t>6717970</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6778117</t>
+          <t>6778894</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>964</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9017</t>
+          <t>9851</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15814</t>
+          <t>15311</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6914</t>
+          <t>6778</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21062</t>
+          <t>21353</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>410446</t>
+          <t>409612</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>418489</t>
+          <t>418499</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>379941</t>
+          <t>380444</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>391497</t>
+          <t>391103</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>794156</t>
+          <t>793865</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>808304</t>
+          <t>808440</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10878</t>
+          <t>10634</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27259</t>
+          <t>27702</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51063</t>
+          <t>50154</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30811</t>
+          <t>30688</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55717</t>
+          <t>54381</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>579618</t>
+          <t>579862</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>589446</t>
+          <t>589455</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>512481</t>
+          <t>513390</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>536285</t>
+          <t>535842</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1098323</t>
+          <t>1099659</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1123229</t>
+          <t>1123352</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15963</t>
+          <t>15713</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12033</t>
+          <t>12248</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31401</t>
+          <t>30964</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18133</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42358</t>
+          <t>39198</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>653134</t>
+          <t>653384</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>665929</t>
+          <t>666038</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>629985</t>
+          <t>630422</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>649353</t>
+          <t>649138</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1288125</t>
+          <t>1291285</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1312350</t>
+          <t>1311734</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>6166</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20216</t>
+          <t>19657</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23829</t>
+          <t>23869</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47510</t>
+          <t>47976</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34624</t>
+          <t>34657</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62240</t>
+          <t>62705</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>625832</t>
+          <t>626391</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>639949</t>
+          <t>639882</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>601567</t>
+          <t>601101</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>625248</t>
+          <t>625208</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1232885</t>
+          <t>1232420</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1260501</t>
+          <t>1260468</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18876</t>
+          <t>19854</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23649</t>
+          <t>24107</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48154</t>
+          <t>48735</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33895</t>
+          <t>33218</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62777</t>
+          <t>63314</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>459042</t>
+          <t>458064</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>472681</t>
+          <t>472555</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>448695</t>
+          <t>448114</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>473200</t>
+          <t>472742</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>911990</t>
+          <t>911453</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>940872</t>
+          <t>941549</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10112</t>
+          <t>9648</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16487</t>
+          <t>16298</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35331</t>
+          <t>34973</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19142</t>
+          <t>19026</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39311</t>
+          <t>40385</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>324218</t>
+          <t>324682</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>333321</t>
+          <t>333326</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>342431</t>
+          <t>342789</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>361275</t>
+          <t>361464</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>672781</t>
+          <t>671707</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>692950</t>
+          <t>693066</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12218</t>
+          <t>12310</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23834</t>
+          <t>24527</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48214</t>
+          <t>48540</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28830</t>
+          <t>29692</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55493</t>
+          <t>55734</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>244780</t>
+          <t>244688</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>254367</t>
+          <t>254365</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>351955</t>
+          <t>351629</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>376335</t>
+          <t>375642</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>601674</t>
+          <t>601433</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>628337</t>
+          <t>627475</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>35392</t>
+          <t>35615</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>62858</t>
+          <t>64238</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>169038</t>
+          <t>166148</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>225855</t>
+          <t>223414</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>211957</t>
+          <t>212211</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>280336</t>
+          <t>273862</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3331492</t>
+          <t>3330112</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3358958</t>
+          <t>3358735</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3318687</t>
+          <t>3321128</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3375504</t>
+          <t>3378394</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6658556</t>
+          <t>6665030</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6726935</t>
+          <t>6726681</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12898</t>
+          <t>12839</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29997</t>
+          <t>28833</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>31835</t>
+          <t>36979</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19603</t>
+          <t>23777</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48410</t>
+          <t>55165</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>44733</t>
+          <t>49818</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28981</t>
+          <t>32100</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67851</t>
+          <t>73997</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>386924</t>
+          <t>393217</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>369825</t>
+          <t>377223</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>395430</t>
+          <t>401960</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>281365</t>
+          <t>325533</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>264790</t>
+          <t>307347</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>293597</t>
+          <t>338735</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>668289</t>
+          <t>718750</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>645171</t>
+          <t>694571</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>684041</t>
+          <t>736468</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399822</t>
+          <t>406056</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399822</t>
+          <t>406056</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399822</t>
+          <t>406056</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713022</t>
+          <t>768568</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713022</t>
+          <t>768568</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713022</t>
+          <t>768568</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20154</t>
+          <t>21903</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11348</t>
+          <t>12237</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33225</t>
+          <t>35355</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>49161</t>
+          <t>52486</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29823</t>
+          <t>39625</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66597</t>
+          <t>68531</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>69315</t>
+          <t>74390</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51646</t>
+          <t>56246</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90949</t>
+          <t>93424</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>403393</t>
+          <t>454987</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>390322</t>
+          <t>441535</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>412199</t>
+          <t>464653</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>462343</t>
+          <t>448597</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>444907</t>
+          <t>432552</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>481681</t>
+          <t>461458</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>865736</t>
+          <t>903583</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>844102</t>
+          <t>884549</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>883405</t>
+          <t>921727</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,25%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>30303</t>
+          <t>30769</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20470</t>
+          <t>19932</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43923</t>
+          <t>43971</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>56693</t>
+          <t>65103</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45226</t>
+          <t>53185</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69034</t>
+          <t>78714</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>86997</t>
+          <t>95872</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72033</t>
+          <t>79986</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104824</t>
+          <t>113465</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>506035</t>
+          <t>590068</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>492415</t>
+          <t>576866</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515868</t>
+          <t>600905</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>483680</t>
+          <t>554872</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>471339</t>
+          <t>541261</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>495147</t>
+          <t>566790</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>989715</t>
+          <t>1144940</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>971888</t>
+          <t>1127347</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1004679</t>
+          <t>1160826</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,55%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>540373</t>
+          <t>619975</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>540373</t>
+          <t>619975</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>540373</t>
+          <t>619975</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1076712</t>
+          <t>1240812</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1076712</t>
+          <t>1240812</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1076712</t>
+          <t>1240812</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41062</t>
+          <t>43553</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18009</t>
+          <t>31491</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65574</t>
+          <t>58801</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>104173</t>
+          <t>107487</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86707</t>
+          <t>92016</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124822</t>
+          <t>121379</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>145235</t>
+          <t>151040</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90288</t>
+          <t>131840</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>183963</t>
+          <t>171868</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>845668</t>
+          <t>655969</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>821156</t>
+          <t>640721</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>868721</t>
+          <t>668031</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>607591</t>
+          <t>628287</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>586942</t>
+          <t>614395</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>625057</t>
+          <t>643758</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1453259</t>
+          <t>1284255</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1414531</t>
+          <t>1263427</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1508206</t>
+          <t>1303455</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>90,81%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>886730</t>
+          <t>699522</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>886730</t>
+          <t>699522</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>886730</t>
+          <t>699522</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711764</t>
+          <t>735774</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>711764</t>
+          <t>735774</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>711764</t>
+          <t>735774</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1598494</t>
+          <t>1435295</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1598494</t>
+          <t>1435295</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1598494</t>
+          <t>1435295</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>23723</t>
+          <t>25489</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16340</t>
+          <t>17297</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34390</t>
+          <t>36177</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>65948</t>
+          <t>74802</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54427</t>
+          <t>63211</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77659</t>
+          <t>88646</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>89671</t>
+          <t>100291</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76686</t>
+          <t>85867</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>106526</t>
+          <t>116890</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>536514</t>
+          <t>582870</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>525847</t>
+          <t>572182</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>543897</t>
+          <t>591062</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>478780</t>
+          <t>531963</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>467069</t>
+          <t>518119</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>490301</t>
+          <t>543554</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1015293</t>
+          <t>1114833</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>998438</t>
+          <t>1098234</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1028278</t>
+          <t>1129257</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,93%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544728</t>
+          <t>606765</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544728</t>
+          <t>606765</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544728</t>
+          <t>606765</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1104964</t>
+          <t>1215124</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1104964</t>
+          <t>1215124</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1104964</t>
+          <t>1215124</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13228</t>
+          <t>13584</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>8457</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>21017</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>34911</t>
+          <t>38895</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14420</t>
+          <t>31122</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58053</t>
+          <t>49080</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>48140</t>
+          <t>52480</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24929</t>
+          <t>43158</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>65129</t>
+          <t>64994</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>354219</t>
+          <t>392627</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>347209</t>
+          <t>385194</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>359546</t>
+          <t>397754</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>573457</t>
+          <t>400271</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>550315</t>
+          <t>390086</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>593948</t>
+          <t>408044</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>927674</t>
+          <t>792898</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>910685</t>
+          <t>780384</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>950885</t>
+          <t>802220</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>94,89%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975814</t>
+          <t>845378</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975814</t>
+          <t>845378</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975814</t>
+          <t>845378</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>12126</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>7588</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17557</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>43402</t>
+          <t>46703</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34862</t>
+          <t>38105</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51836</t>
+          <t>56966</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>54736</t>
+          <t>58828</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>45432</t>
+          <t>49223</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>66424</t>
+          <t>71406</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>271426</t>
+          <t>298072</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>265202</t>
+          <t>291496</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>275489</t>
+          <t>302610</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>381829</t>
+          <t>417259</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>373395</t>
+          <t>406996</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>390369</t>
+          <t>425857</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>653254</t>
+          <t>715332</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>641566</t>
+          <t>702754</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>662558</t>
+          <t>724937</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,64%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425231</t>
+          <t>463962</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425231</t>
+          <t>463962</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425231</t>
+          <t>463962</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707990</t>
+          <t>774160</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707990</t>
+          <t>774160</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707990</t>
+          <t>774160</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>152702</t>
+          <t>160263</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>115766</t>
+          <t>133411</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>182537</t>
+          <t>188991</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>386125</t>
+          <t>422455</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>325032</t>
+          <t>389366</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>430155</t>
+          <t>457124</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>538827</t>
+          <t>582717</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>470235</t>
+          <t>545152</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>597952</t>
+          <t>628725</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3304178</t>
+          <t>3367810</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3274343</t>
+          <t>3339082</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3341114</t>
+          <t>3394662</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3269043</t>
+          <t>3306783</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3225013</t>
+          <t>3272114</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3330136</t>
+          <t>3339872</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6573221</t>
+          <t>6674593</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6514096</t>
+          <t>6628585</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6641813</t>
+          <t>6712158</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3456880</t>
+          <t>3528073</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3456880</t>
+          <t>3528073</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3456880</t>
+          <t>3528073</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3655168</t>
+          <t>3729238</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3655168</t>
+          <t>3729238</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3655168</t>
+          <t>3729238</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7112048</t>
+          <t>7257310</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7112048</t>
+          <t>7257310</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7112048</t>
+          <t>7257310</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
